--- a/从零开始学Slots/从零开始学Slots-21-数值篇-不规则窗口(1).xlsx
+++ b/从零开始学Slots/从零开始学Slots-21-数值篇-不规则窗口(1).xlsx
@@ -9736,6 +9736,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N190" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -10830,5 +10833,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M91" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-21-数值篇-不规则窗口(1).xlsx
+++ b/从零开始学Slots/从零开始学Slots-21-数值篇-不规则窗口(1).xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="235">
   <si>
     <r>
       <rPr>
@@ -8553,7 +8553,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -8680,6 +8680,10 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -10353,8 +10357,8 @@
         <f aca="false">C38/D38</f>
         <v>0.052734375</v>
       </c>
-      <c r="G38" s="19" t="s">
-        <v>186</v>
+      <c r="G38" s="32">
+        <v>27</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10376,8 +10380,8 @@
         <f aca="false">C39/D39</f>
         <v>0.052734375</v>
       </c>
-      <c r="G39" s="19" t="s">
-        <v>186</v>
+      <c r="G39" s="32">
+        <v>27</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10705,8 +10709,8 @@
         <f aca="false">IF(B9=B8^B6,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="C63" s="19" t="s">
-        <v>221</v>
+      <c r="C63" s="32">
+        <v>512</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/从零开始学Slots/从零开始学Slots-21-数值篇-不规则窗口(1).xlsx
+++ b/从零开始学Slots/从零开始学Slots-21-数值篇-不规则窗口(1).xlsx
@@ -8364,12 +8364,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="0.0000%"/>
+    <numFmt numFmtId="169" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -8553,7 +8554,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -8683,6 +8684,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10330,7 +10339,7 @@
         <f aca="false">$B$9</f>
         <v>512</v>
       </c>
-      <c r="E37" s="20" t="n">
+      <c r="E37" s="33" t="n">
         <f aca="false">C37/D37</f>
         <v>0.052734375</v>
       </c>
@@ -10353,7 +10362,7 @@
         <f aca="false">$B$9</f>
         <v>512</v>
       </c>
-      <c r="E38" s="20" t="n">
+      <c r="E38" s="33" t="n">
         <f aca="false">C38/D38</f>
         <v>0.052734375</v>
       </c>
@@ -10376,7 +10385,7 @@
         <f aca="false">$B$9</f>
         <v>512</v>
       </c>
-      <c r="E39" s="20" t="n">
+      <c r="E39" s="33" t="n">
         <f aca="false">C39/D39</f>
         <v>0.052734375</v>
       </c>
@@ -10399,7 +10408,7 @@
         <f aca="false">$B$9</f>
         <v>512</v>
       </c>
-      <c r="E40" s="20" t="n">
+      <c r="E40" s="33" t="n">
         <f aca="false">C40/D40</f>
         <v>0.005859375</v>
       </c>
@@ -10449,7 +10458,7 @@
       <c r="B44" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="C44" s="20" t="n">
+      <c r="C44" s="33" t="n">
         <f aca="false">E37</f>
         <v>0.052734375</v>
       </c>
@@ -10471,7 +10480,7 @@
       <c r="B45" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="C45" s="20" t="n">
+      <c r="C45" s="33" t="n">
         <f aca="false">E38</f>
         <v>0.052734375</v>
       </c>
@@ -10493,7 +10502,7 @@
       <c r="B46" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="C46" s="20" t="n">
+      <c r="C46" s="33" t="n">
         <f aca="false">E39</f>
         <v>0.052734375</v>
       </c>
@@ -10552,7 +10561,7 @@
       <c r="A51" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="B51" s="23" t="n">
+      <c r="B51" s="34" t="n">
         <f aca="false">E40</f>
         <v>0.005859375</v>
       </c>
